--- a/artfynd/A 39105-2024 artfynd.xlsx
+++ b/artfynd/A 39105-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>16750637</v>
       </c>
       <c r="B2" t="n">
-        <v>99885</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480944.0323794165</v>
+        <v>480944</v>
       </c>
       <c r="R2" t="n">
-        <v>6619795.241687876</v>
+        <v>6619795</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>1986-06-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1986-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,6 +789,241 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>112720488</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102755</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1879</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Trollsmultron</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Drymocallis rupestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soják</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sikberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>480932</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6619804</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112777497</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100164</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222654</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunag</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rhynchospora fusca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) W. T. Aiton</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Siken, i norr, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>481156</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6619722</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>T-Häl-0150</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gungflyn och flytöar i Sikens norra del. På västra sidan. Över stor yta. Räknad och uppskattat antal inom ca. 75 m från koordinat. Kan även finnas längre norrut och på östra sidan av Sikens norra del.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gungfly</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39105-2024 artfynd.xlsx
+++ b/artfynd/A 39105-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16750637</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112720488</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,8 +1039,18 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112777497</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>